--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post DFS_HRM-2031-0120/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post DFS_HRM-2031-0120/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.12145</v>
+        <v>16.54117</v>
       </c>
       <c r="D2" t="n">
-        <v>16.22688</v>
+        <v>16.43855</v>
       </c>
       <c r="E2" t="n">
-        <v>16.5218</v>
+        <v>16.53969</v>
       </c>
       <c r="F2" t="n">
-        <v>41.96895</v>
+        <v>43.07155</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04932</v>
+        <v>0.05055</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8089</v>
+        <v>1.83545</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.00215</v>
+        <v>16.75259</v>
       </c>
       <c r="D3" t="n">
-        <v>16.38353</v>
+        <v>16.40828</v>
       </c>
       <c r="E3" t="n">
-        <v>16.42082</v>
+        <v>16.43993</v>
       </c>
       <c r="F3" t="n">
-        <v>42.23615</v>
+        <v>42.96783</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04995</v>
+        <v>0.04981</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81542</v>
+        <v>1.84057</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.79641</v>
+        <v>16.74445</v>
       </c>
       <c r="D4" t="n">
-        <v>16.52069</v>
+        <v>16.68081</v>
       </c>
       <c r="E4" t="n">
-        <v>16.85119</v>
+        <v>16.71576</v>
       </c>
       <c r="F4" t="n">
-        <v>43.01579</v>
+        <v>41.84828</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04935</v>
+        <v>0.05119</v>
       </c>
       <c r="H4" t="n">
-        <v>1.79954</v>
+        <v>1.84395</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.5492</v>
+        <v>16.567</v>
       </c>
       <c r="D6" t="n">
-        <v>15.89538</v>
+        <v>16.04462</v>
       </c>
       <c r="E6" t="n">
-        <v>16.41709</v>
+        <v>16.066</v>
       </c>
       <c r="F6" t="n">
-        <v>21.6798</v>
+        <v>22.11652</v>
       </c>
       <c r="G6" t="n">
-        <v>33.15743</v>
+        <v>33.91323</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.84131</v>
+        <v>16.70132</v>
       </c>
       <c r="D7" t="n">
-        <v>16.11299</v>
+        <v>15.96164</v>
       </c>
       <c r="E7" t="n">
-        <v>16.76906</v>
+        <v>16.16684</v>
       </c>
       <c r="F7" t="n">
-        <v>21.64025</v>
+        <v>21.36923</v>
       </c>
       <c r="G7" t="n">
-        <v>34.48652</v>
+        <v>34.02415</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.40672</v>
+        <v>16.70566</v>
       </c>
       <c r="D8" t="n">
-        <v>16.09718</v>
+        <v>16.11434</v>
       </c>
       <c r="E8" t="n">
-        <v>16.2622</v>
+        <v>16.3064</v>
       </c>
       <c r="F8" t="n">
-        <v>21.96337</v>
+        <v>21.90962</v>
       </c>
       <c r="G8" t="n">
-        <v>35.01903</v>
+        <v>34.25513</v>
       </c>
     </row>
   </sheetData>
